--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.7957307832701</v>
+        <v>6.629306252281392</v>
       </c>
       <c r="D2" t="n">
-        <v>40.62216400365904</v>
+        <v>6.601101650594595</v>
       </c>
       <c r="E2" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F2" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.45024714973532</v>
+        <v>4.13566516183199</v>
       </c>
       <c r="D3" t="n">
-        <v>25.28819464044571</v>
+        <v>4.109331629072427</v>
       </c>
       <c r="E3" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F3" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.18940348752157</v>
+        <v>5.555778066722254</v>
       </c>
       <c r="D4" t="n">
-        <v>34.35770039157387</v>
+        <v>5.583126313630754</v>
       </c>
       <c r="E4" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F4" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.51217016585708</v>
+        <v>5.445727651951776</v>
       </c>
       <c r="D5" t="n">
-        <v>33.68411049653729</v>
+        <v>5.47366795568731</v>
       </c>
       <c r="E5" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F5" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.29339107294368</v>
+        <v>5.897676049353348</v>
       </c>
       <c r="D6" t="n">
-        <v>36.28189690871966</v>
+        <v>5.895808247666944</v>
       </c>
       <c r="E6" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F6" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.09002102403707</v>
+        <v>5.539628416406024</v>
       </c>
       <c r="D7" t="n">
-        <v>34.25176345519053</v>
+        <v>5.565911561468462</v>
       </c>
       <c r="E7" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F7" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.56354675951961</v>
+        <v>6.916576348421937</v>
       </c>
       <c r="D8" t="n">
-        <v>42.58473576289494</v>
+        <v>6.920019561470427</v>
       </c>
       <c r="E8" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F8" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93020063579218</v>
+        <v>7.138657603316228</v>
       </c>
       <c r="D9" t="n">
-        <v>44.09129405697882</v>
+        <v>7.164835284259058</v>
       </c>
       <c r="E9" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F9" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.24906130777035</v>
+        <v>7.027972462512682</v>
       </c>
       <c r="D10" t="n">
-        <v>43.39030338879343</v>
+        <v>7.050924300678933</v>
       </c>
       <c r="E10" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F10" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.33633317857631</v>
+        <v>7.204654141518651</v>
       </c>
       <c r="D11" t="n">
-        <v>44.40779246260702</v>
+        <v>7.216266275173641</v>
       </c>
       <c r="E11" t="n">
-        <v>5.844795498364853</v>
+        <v>0.9497792684842886</v>
       </c>
       <c r="F11" t="n">
-        <v>5.877846668313897</v>
+        <v>0.9551500836010086</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
